--- a/artifacts/api-server/data/fms_live.xlsx
+++ b/artifacts/api-server/data/fms_live.xlsx
@@ -179,7 +179,7 @@
     <t>RAPORT FINANCIAR — FMS PRO</t>
   </si>
   <si>
-    <t>Përditësuar: 31.10.2026, 6:45:22 m.d.</t>
+    <t>Përditësuar: 31.10.2026, 6:51:11 m.d.</t>
   </si>
   <si>
     <t/>
